--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T10:38:49+00:00</t>
+    <t>2025-02-11T11:03:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:03:37+00:00</t>
+    <t>2025-02-11T12:08:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,10 +84,12 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Libellé court de l'organisation
++The Organization short name</t>
+  </si>
+  <si>
     <t>Purpose</t>
-  </si>
-  <si>
-    <t>The Organization short name | Libellé court de l'organisation</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -259,9 +261,6 @@
 </t>
   </si>
   <si>
-    <t>An Extension</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
@@ -297,6 +296,9 @@
   <si>
     <t xml:space="preserve">Extension
 </t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -580,15 +582,15 @@
       <c r="A13" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>23</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>24</v>
       </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -847,7 +849,7 @@
         <v>9</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -907,10 +909,10 @@
         <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ2" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="AJ2" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>77</v>
@@ -918,10 +920,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -932,25 +934,25 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1001,13 +1003,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -1016,15 +1018,15 @@
         <v>77</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1047,13 +1049,13 @@
         <v>77</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>31</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1116,7 +1118,7 @@
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -1135,10 +1137,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
@@ -1212,10 +1214,10 @@
         <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
@@ -1243,19 +1245,19 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="H6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K6" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L6" t="s" s="2">
         <v>104</v>
@@ -1318,7 +1320,7 @@
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:08:53+00:00</t>
+    <t>2025-02-11T15:31:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:31:42+00:00</t>
+    <t>2025-02-11T17:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:07:06+00:00</t>
+    <t>2025-02-11T17:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:08:15+00:00</t>
+    <t>2025-02-11T17:29:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
